--- a/design/monthly-reports/2026년 10월 상품 원가표.xlsx
+++ b/design/monthly-reports/2026년 10월 상품 원가표.xlsx
@@ -454,7 +454,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>액상덕후 2026년 10월 상품 원가표 — 10월 1~29일 매출 집계 주문 기준 · 노보 병당 6,000원</t>
+          <t>액상덕후 2026년 10월 상품 원가표 — 10월 1~29일 매출 집계 주문 기준 · 노보 병당 6,000원 · 빌런 · 덕후 액상 병당 2,200원 · 젤로 크리스탈 기기 원가 제외</t>
         </is>
       </c>
     </row>
@@ -574,13 +574,13 @@
         <v>4346023</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3579380</v>
+        <v>949000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.823598954722513</v>
+        <v>0.2183605563063058</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>51500</v>
+        <v>11000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -784,13 +784,13 @@
         <v>1519169</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1384360</v>
+        <v>712030</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9112613540692313</v>
+        <v>0.4686970310742254</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>15650</v>
+        <v>11000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         <v>776417</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>574420</v>
+        <v>233100</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7398343931160704</v>
+        <v>0.3002252655467358</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>66200</v>
+        <v>25600</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1477,13 +1477,13 @@
         <v>173359</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>50080</v>
+        <v>35200</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.2888803004170536</v>
+        <v>0.2030468565231687</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3130</v>
+        <v>2200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2226,13 +2226,13 @@
         <v>59142</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>30780</v>
+        <v>13200</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.5204423252510906</v>
+        <v>0.2231916404585574</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>5130</v>
+        <v>2200</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         <v>59131</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>31380</v>
+        <v>13200</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.5306861037357731</v>
+        <v>0.2232331602712621</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>5230</v>
+        <v>2200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2296,13 +2296,13 @@
         <v>54408</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>27850</v>
+        <v>11000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.5118732539332451</v>
+        <v>0.2021761505660932</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>5570</v>
+        <v>2200</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         <v>39612</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>21200</v>
+        <v>8800</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.5351913561547006</v>
+        <v>0.2221549025547814</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>5300</v>
+        <v>2200</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3479,13 +3479,13 @@
         <v>21800</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>10540</v>
+        <v>4400</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.4834862385321101</v>
+        <v>0.2018348623853211</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>5270</v>
+        <v>2200</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
         <v>44753716</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>25866056</v>
+        <v>22135996</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>0.5779644309312773</v>
+        <v>0.494618055850379</v>
       </c>
       <c r="F146" s="3" t="n"/>
       <c r="H146" s="3" t="n"/>
@@ -4731,7 +4731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4765,58 +4765,82 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>그 밖 상품</t>
+          <t>빌런 · 흑염룡 · 멘솔쨩</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>베이프렌드 본점 마스터(________MASTER____261009) 원가</t>
+          <t>병당 2,200원 (대표 확인 10/30)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>마스터에 없는 상품</t>
+          <t>젤로 크리스탈 패키지(5병 · 10병)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>기존 워드프레스 원가표 값 — 「원가 근거: 잠정 포함」</t>
+          <t>기기 원가는 넣지 않고 들어간 액상 · 팟만 셈 (대표 확인 10/30)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>묶음</t>
+          <t>그 밖 상품</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>들어간 병 수 × 병당 원가 + 기기 · 팟</t>
+          <t>베이프렌드 본점 마스터(________MASTER____261009) 원가</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>마스터에 없는 상품</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>할인 · 환불 뒤 상품 금액, 배송비 제외 · 취소 · 미입금 제외</t>
+          <t>기존 워드프레스 원가표 값 — 「원가 근거: 잠정 포함」</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>묶음</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>들어간 병 수 × 병당 원가 + 기기 · 팟</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>할인 · 환불 뒤 상품 금액, 배송비 제외 · 취소 · 미입금 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>기간</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-10-01 ~ 10-29 접수 주문 (10/30 조회)</t>
         </is>

--- a/design/monthly-reports/2026년 10월 상품 원가표.xlsx
+++ b/design/monthly-reports/2026년 10월 상품 원가표.xlsx
@@ -454,7 +454,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>액상덕후 2026년 10월 상품 원가표 — 10월 1~29일 매출 집계 주문 기준 · 노보 병당 6,000원 · 빌런 · 덕후 액상 병당 2,200원 · 젤로 크리스탈 기기 원가 제외</t>
+          <t>액상덕후 2026년 10월 상품 원가표 — 10월 1~29일 매출 집계 주문 기준 · 노보 병당 6,000원 · 빌런 · 덕후 액상 병당 2,200원 · 화이트아웃 3,500원 · 젤로 크리스탈 기기 원가 제외</t>
         </is>
       </c>
     </row>
@@ -574,10 +574,10 @@
         <v>4346023</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>949000</v>
+        <v>905500</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2183605563063058</v>
+        <v>0.2083514054113381</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>11000</v>
@@ -938,13 +938,13 @@
         <v>810130</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>528000</v>
+        <v>378000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6517472504412872</v>
+        <v>0.4665917815659215</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>776417</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>233100</v>
+        <v>225600</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3002252655467358</v>
+        <v>0.2905655079680121</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>25600</v>
@@ -1057,13 +1057,13 @@
         <v>507617</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>306546</v>
+        <v>216546</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6038923046312475</v>
+        <v>0.4265932780029038</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2394,13 +2394,13 @@
         <v>47593</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>22000</v>
+        <v>17500</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.4622528523102137</v>
+        <v>0.3677011325194882</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2660,13 +2660,13 @@
         <v>39800</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.4271356783919598</v>
+        <v>0.3517587939698493</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         <v>14900</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>0.3355704697986577</v>
+        <v>0.2348993288590604</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3949,13 +3949,13 @@
         <v>13132</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>0.3807493146512336</v>
+        <v>0.2665245202558635</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4334,13 +4334,13 @@
         <v>9368</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>0.533731853116994</v>
+        <v>0.3736122971818958</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
         <v>44753716</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>22135996</v>
+        <v>21832996</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>0.494618055850379</v>
+        <v>0.487847668336636</v>
       </c>
       <c r="F146" s="3" t="n"/>
       <c r="H146" s="3" t="n"/>
@@ -4731,7 +4731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4777,70 +4777,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>젤로 크리스탈 패키지(5병 · 10병)</t>
+          <t>화이트아웃</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>기기 원가는 넣지 않고 들어간 액상 · 팟만 셈 (대표 확인 10/30)</t>
+          <t>병당 3,500원 (대표 확인 10/30)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>그 밖 상품</t>
+          <t>젤로 크리스탈 패키지(5병 · 10병)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>베이프렌드 본점 마스터(________MASTER____261009) 원가</t>
+          <t>기기 원가는 넣지 않고 들어간 액상 · 팟만 셈 (대표 확인 10/30)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>마스터에 없는 상품</t>
+          <t>그 밖 상품</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>기존 워드프레스 원가표 값 — 「원가 근거: 잠정 포함」</t>
+          <t>베이프렌드 본점 마스터(________MASTER____261009) 원가</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>묶음</t>
+          <t>마스터에 없는 상품</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>들어간 병 수 × 병당 원가 + 기기 · 팟</t>
+          <t>기존 워드프레스 원가표 값 — 「원가 근거: 잠정 포함」</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>할인 · 환불 뒤 상품 금액, 배송비 제외 · 취소 · 미입금 제외</t>
+          <t>들어간 병 수 × 병당 원가 + 기기 · 팟</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>할인 · 환불 뒤 상품 금액, 배송비 제외 · 취소 · 미입금 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>기간</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-10-01 ~ 10-29 접수 주문 (10/30 조회)</t>
         </is>
